--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q40_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01069670807980125</v>
+        <v>0.009740825067936568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01069670807980125</v>
+        <v>0.009740825067936568</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0104859113837148</v>
+        <v>0.009540452404991831</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0104859113837148</v>
+        <v>0.009540452404991831</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0120368726145675</v>
+        <v>0.01106811158904024</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0120368726145675</v>
+        <v>0.01106811158904024</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01669597764561316</v>
+        <v>0.015528731543383</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01669597764561316</v>
+        <v>0.015528731543383</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02387705832363716</v>
+        <v>0.02227565155193557</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02387705832363716</v>
+        <v>0.02227565155193557</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03164929956975893</v>
+        <v>0.02941962521542768</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03164929956975893</v>
+        <v>0.02941962521542768</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04075930359822671</v>
+        <v>0.03779682043460524</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04075930359822671</v>
+        <v>0.03779682043460524</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0512239046433242</v>
+        <v>0.04754298958254542</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0512239046433242</v>
+        <v>0.04754298958254542</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.06041798876257462</v>
+        <v>0.05616631880317469</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06041798876257462</v>
+        <v>0.05616631880317469</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06700392895174941</v>
+        <v>0.06232382265246864</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06700392895174941</v>
+        <v>0.06232382265246864</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.07036345899681599</v>
+        <v>0.06543358884354084</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07036345899681599</v>
+        <v>0.06543358884354084</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.07174529550091582</v>
+        <v>0.06668159938138163</v>
       </c>
       <c r="C13" t="n">
-        <v>0.07174529550091582</v>
+        <v>0.06668159938138163</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.07088057991435801</v>
+        <v>0.06585572002902187</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07088057991435801</v>
+        <v>0.06585572002902187</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.06934253409072512</v>
+        <v>0.06442912607583062</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06934253409072512</v>
+        <v>0.06442912607583062</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.06616563541748981</v>
+        <v>0.06147553660526871</v>
       </c>
       <c r="C16" t="n">
-        <v>0.06616563541748981</v>
+        <v>0.06147553660526871</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06486296643218349</v>
+        <v>0.06025014682125931</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06486296643218349</v>
+        <v>0.06025014682125931</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06207457921764967</v>
+        <v>0.05773053071061488</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06207457921764967</v>
+        <v>0.05773053071061488</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06042239453942372</v>
+        <v>0.05617965632802187</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06042239453942372</v>
+        <v>0.05617965632802187</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.05921381867505458</v>
+        <v>0.05511384742025301</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05921381867505458</v>
+        <v>0.05511384742025301</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0580838189223146</v>
+        <v>0.05405351190590102</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0580838189223146</v>
+        <v>0.05405351190590102</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
